--- a/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
@@ -898,16 +898,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-1.1</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -915,16 +933,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>2.03</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1034,16 +1070,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>112.115</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
@@ -647,24 +647,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BCEAO Monetary Policy Committee</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>09-Sep-26</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BCEAO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>09-Sep-26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BCEAO main rate; marginal lending 5.0%</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -704,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>Institut National de la Statistique (IHPC)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -740,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -788,10 +784,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>30-Jun-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Central government debt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance</t>
+          <t>IMF / Ministry of Finance (budgeted deficit)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
+          <t>EFF/ECF (40-month, US$3.5B) and RSF (US$1.3B); final reviews completed Jun-26</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1286,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1310,6 +1310,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>2028F</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1322,7 +1327,8 @@
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1336,9 +1342,10 @@
       <c r="C3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IMF, Jun-26</t>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IMF, 30-Jun-26</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1357,8 @@
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1360,7 +1368,8 @@
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1368,11 +1377,20 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>-3</v>
+      </c>
       <c r="C6" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF / Ministry of Finance, 30-Jun-26 (2025 outturn at WAEMU 3.0% ceiling; 2028F is the commitment to return to the ceiling)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1382,7 +1400,8 @@
       </c>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1396,9 +1415,10 @@
       <c r="C8" s="2" t="n">
         <v>55.1</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IMF / Ministry of Finance, Jun-26</t>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IMF / Ministry of Finance, 30-Jun-26</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1430,8 @@
       </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1420,7 +1441,8 @@
       </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1430,7 +1452,8 @@
       </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1440,7 +1463,8 @@
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Institut National de la Statistique (IHPC)</t>
+          <t>INS Cote d'Ivoire, IHPC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt</t>
+          <t>Government debt, projection; WAEMU ceiling 70%</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026 budget</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance (budgeted deficit)</t>
+          <t>IMF / Ministry of Finance</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -921,11 +921,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -956,11 +952,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1071,7 +1063,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>112.115</v>
+        <v>112.1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1093,11 +1085,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1263,11 +1251,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF (40-month, US$3.5B) and RSF (US$1.3B); final reviews completed Jun-26</t>
+          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed Jun-26</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1326,9 +1314,15 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
+      <c r="C2" s="2" t="n">
+        <v>112.1</v>
+      </c>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1345,7 +1339,7 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IMF, 30-Jun-26</t>
+          <t>IMF, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1367,9 +1361,15 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
+        <v>-1.1</v>
+      </c>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, 30-Jun-26 (2025 outturn at WAEMU 3.0% ceiling; 2028F is the commitment to return to the ceiling)</t>
+          <t>IMF / Ministry of Finance, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, 30-Jun-26</t>
+          <t>IMF / Ministry of Finance, Jun-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cote_d_Ivoire_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS Cote d'Ivoire, IHPC</t>
+          <t>INS Côte d'Ivoire, IHPC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Government debt, projection; WAEMU ceiling 70%</t>
+          <t>Government debt, projection</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026 budget</t>
+          <t>2026 (budgeted)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed Jun-26</t>
+          <t>EFF/ECF (final sixth review completed) and RSF (fifth review completed)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, Jun-26</t>
+          <t>IMF / Ministry of Finance, Jun-26 (2026 budgeted deficit)</t>
         </is>
       </c>
     </row>
